--- a/output/2026-10-04_19_Malesia_Selangor_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-10-04_19_Malesia_Selangor_Depolverazione_Trattamento_aria.xlsx
@@ -501,7 +501,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Engineering/contracting/manifattura dal 1983, one-stop per controllo inquinamento aria (dust collector, scrubber, ESP, ventilazione). Confermato via sito ufficiale e AHK Malaysia. Profilo misto produttore/EPC/fornitore B2B verso industrie terze.</t>
+          <t>Engineering/contracting/manifattura dal 1983, one-stop per controllo inquinamento aria (dust collector, scrubber, ESP, ventilazione). Confermato via sito ufficiale e AHK Malaysia. Profilo misto produttore/EPC/fornitore B2B verso industrie terze. [DUPLICATO — vedi anche: 2026-09-30_16_Malesia_Johor_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Importatore/distributore dal 1996 di spazzatrici industriali, lavasciuga e aspiratori industriali; rappresenta marchi esteri incl. DISAB-TELLA (Svezia). Confermato via sito ufficiale, AHK Malaysia, sgpgrid.</t>
+          <t>Importatore/distributore dal 1996 di spazzatrici industriali, lavasciuga e aspiratori industriali; rappresenta marchi esteri incl. DISAB-TELLA (Svezia). Confermato via sito ufficiale, AHK Malaysia, sgpgrid. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Importatore/distributore macchine pulizia industriale; brand rappresentati: Floormac, Fasa, Nilfisk, Tennant, Karcher, 3M, Viper, Sulo, Delfin, Orapi. ATTENZIONE: il sito dichiara di rappresentare gia' Delfin (gruppo Dupuy/Delfin) in Malesia - possibile conflitto d'interesse, verificare prima di contatto commerciale.</t>
+          <t>Importatore/distributore macchine pulizia industriale; brand rappresentati: Floormac, Fasa, Nilfisk, Tennant, Karcher, 3M, Viper, Sulo, Delfin, Orapi. ATTENZIONE: il sito dichiara di rappresentare gia' Delfin (gruppo Dupuy/Delfin) in Malesia - possibile conflitto d'interesse, verificare prima di contatto commerciale. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -600,7 +600,6 @@
           <t>KLENCO (M) SDN BHD</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
           <t>Selangor (Shah Alam)</t>
@@ -611,11 +610,9 @@
           <t>Depolverazione / Trattamento aria (pulizia industriale)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Distributore indipendente di macchine/chemicals per pulizia industriale/istituzionale dal 1971, leader regionale SE Asia (fonti: sgpgrid, jobstore.my, AHK directory). Dominio klenco.com risulta parcheggiato/in vendita; nessun contatto diretto verificabile.</t>
+          <t>Distributore indipendente di macchine/chemicals per pulizia industriale/istituzionale dal 1971, leader regionale SE Asia (fonti: sgpgrid, jobstore.my, AHK directory). Dominio klenco.com risulta parcheggiato/in vendita; nessun contatto diretto verificabile. [DUPLICATO — vedi anche: 2026-10-02_17_Malesia_Pahang_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -650,10 +647,9 @@
           <t>+603-7846 0340</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Consociata malese del gruppo britannico Elta (dal 2006): vendita, fabbricazione, assemblaggio e distribuzione prodotti di ventilazione industriale; member of Elta Group con rete distributori internazionali, certificazione BSI.</t>
+          <t>Consociata malese del gruppo britannico Elta (dal 2006): vendita, fabbricazione, assemblaggio e distribuzione prodotti di ventilazione industriale; member of Elta Group con rete distributori internazionali, certificazione BSI. [DUPLICATO — vedi anche: 2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
